--- a/논산시청 5일차 - 수업용.xlsx
+++ b/논산시청 5일차 - 수업용.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\05.제출용\YBM\논산시청\강의자료\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\kjmin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A65E438E-B4A5-4B39-93E6-F6999517D742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABF88A13-3786-4ADA-BD05-4C5D1FBD64AD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17390" yWindow="3160" windowWidth="19390" windowHeight="17840" xr2:uid="{2697AA2F-31CB-4C2E-90CB-DA2C4988393A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8628" activeTab="8" xr2:uid="{2697AA2F-31CB-4C2E-90CB-DA2C4988393A}"/>
   </bookViews>
   <sheets>
     <sheet name="표1" sheetId="1" r:id="rId1"/>
@@ -21,36 +21,26 @@
     <sheet name="표6" sheetId="6" r:id="rId6"/>
     <sheet name="표7" sheetId="7" r:id="rId7"/>
     <sheet name="표8" sheetId="8" r:id="rId8"/>
-    <sheet name="표9" sheetId="9" r:id="rId9"/>
-    <sheet name="표10" sheetId="10" r:id="rId10"/>
-    <sheet name="표11" sheetId="11" r:id="rId11"/>
-    <sheet name="표12" sheetId="12" r:id="rId12"/>
-    <sheet name="표13" sheetId="13" r:id="rId13"/>
-    <sheet name="표14" sheetId="14" r:id="rId14"/>
-    <sheet name="표15" sheetId="15" r:id="rId15"/>
+    <sheet name="Sheet1" sheetId="16" r:id="rId9"/>
+    <sheet name="표9" sheetId="9" r:id="rId10"/>
+    <sheet name="표10" sheetId="10" r:id="rId11"/>
+    <sheet name="표11" sheetId="11" r:id="rId12"/>
+    <sheet name="표12" sheetId="12" r:id="rId13"/>
+    <sheet name="표13" sheetId="13" r:id="rId14"/>
+    <sheet name="표14" sheetId="14" r:id="rId15"/>
+    <sheet name="표15" sheetId="15" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="560">
   <si>
     <t>지표</t>
   </si>
@@ -2241,14 +2231,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BD71F37-85ED-4FB4-B4E1-AB995B54E90E}">
   <dimension ref="B4:I15"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="19.08203125" customWidth="1"/>
-    <col min="8" max="8" width="30.4140625" customWidth="1"/>
-    <col min="9" max="9" width="56.6640625" customWidth="1"/>
+    <col min="2" max="2" width="19.09765625" customWidth="1"/>
+    <col min="8" max="8" width="30.3984375" customWidth="1"/>
+    <col min="9" max="9" width="56.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="4" t="s">
         <v>0</v>
       </c>
@@ -2274,7 +2264,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="5" t="s">
         <v>3</v>
       </c>
@@ -2290,7 +2280,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="5" t="s">
         <v>6</v>
       </c>
@@ -2306,7 +2296,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
@@ -2322,7 +2312,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="5" t="s">
         <v>12</v>
       </c>
@@ -2338,7 +2328,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="5" t="s">
         <v>15</v>
       </c>
@@ -2354,7 +2344,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="5" t="s">
         <v>18</v>
       </c>
@@ -2370,7 +2360,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="5" t="s">
         <v>21</v>
       </c>
@@ -2386,7 +2376,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="5" t="s">
         <v>23</v>
       </c>
@@ -2402,7 +2392,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="5" t="s">
         <v>26</v>
       </c>
@@ -2418,7 +2408,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="5" t="s">
         <v>29</v>
       </c>
@@ -2434,7 +2424,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="5" t="s">
         <v>32</v>
       </c>
@@ -2467,88 +2457,108 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D66CB6B7-EAEB-4FA8-A2DF-08B32D04D522}">
-  <dimension ref="B2:G5"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D7B6EB1-DF05-4E63-BE4E-F700AD81F457}">
+  <dimension ref="B2:G6"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="2" spans="2:7" ht="34" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B2" s="4" t="s">
-        <v>455</v>
+        <v>430</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>456</v>
+        <v>431</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>457</v>
+        <v>432</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>458</v>
+        <v>433</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>459</v>
+        <v>434</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.45">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B3" s="5" t="s">
-        <v>461</v>
-      </c>
-      <c r="C3" s="5">
-        <v>40</v>
-      </c>
-      <c r="D3" s="5">
-        <v>35</v>
-      </c>
-      <c r="E3" s="5">
-        <v>55</v>
-      </c>
-      <c r="F3" s="5">
-        <v>10</v>
-      </c>
-      <c r="G3" s="5">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.45">
+        <v>436</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
       <c r="B4" s="5" t="s">
-        <v>462</v>
-      </c>
-      <c r="C4" s="5">
-        <v>45</v>
-      </c>
-      <c r="D4" s="5">
-        <v>40</v>
-      </c>
-      <c r="E4" s="5">
-        <v>70</v>
-      </c>
-      <c r="F4" s="5">
-        <v>10</v>
-      </c>
-      <c r="G4" s="5">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.45">
+        <v>442</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
       <c r="B5" s="5" t="s">
-        <v>463</v>
-      </c>
-      <c r="C5" s="5">
-        <v>50</v>
-      </c>
-      <c r="D5" s="5">
-        <v>45</v>
-      </c>
-      <c r="E5" s="5">
-        <v>80</v>
-      </c>
-      <c r="F5" s="5">
-        <v>10</v>
-      </c>
-      <c r="G5" s="5">
-        <v>185</v>
+        <v>447</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="B6" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>454</v>
       </c>
     </row>
   </sheetData>
@@ -2558,110 +2568,88 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F336CF09-ABF6-4B58-B238-B7578D6DF1E6}">
-  <dimension ref="B2:F7"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D66CB6B7-EAEB-4FA8-A2DF-08B32D04D522}">
+  <dimension ref="B2:G5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="2" spans="2:6" ht="34" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B2" s="4" t="s">
-        <v>243</v>
+        <v>455</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="3" spans="2:6" ht="68" x14ac:dyDescent="0.45">
+        <v>459</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B3" s="5" t="s">
-        <v>468</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>469</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>470</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>471</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" ht="68" x14ac:dyDescent="0.45">
+        <v>461</v>
+      </c>
+      <c r="C3" s="5">
+        <v>40</v>
+      </c>
+      <c r="D3" s="5">
+        <v>35</v>
+      </c>
+      <c r="E3" s="5">
+        <v>55</v>
+      </c>
+      <c r="F3" s="5">
+        <v>10</v>
+      </c>
+      <c r="G3" s="5">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B4" s="5" t="s">
-        <v>473</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>474</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>476</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" ht="51" x14ac:dyDescent="0.45">
+        <v>462</v>
+      </c>
+      <c r="C4" s="5">
+        <v>45</v>
+      </c>
+      <c r="D4" s="5">
+        <v>40</v>
+      </c>
+      <c r="E4" s="5">
+        <v>70</v>
+      </c>
+      <c r="F4" s="5">
+        <v>10</v>
+      </c>
+      <c r="G4" s="5">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B5" s="5" t="s">
-        <v>478</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>479</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>480</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>481</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" ht="51" x14ac:dyDescent="0.45">
-      <c r="B6" s="5" t="s">
-        <v>483</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>484</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>485</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" ht="51" x14ac:dyDescent="0.45">
-      <c r="B7" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>488</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>489</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>490</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>491</v>
+        <v>463</v>
+      </c>
+      <c r="C5" s="5">
+        <v>50</v>
+      </c>
+      <c r="D5" s="5">
+        <v>45</v>
+      </c>
+      <c r="E5" s="5">
+        <v>80</v>
+      </c>
+      <c r="F5" s="5">
+        <v>10</v>
+      </c>
+      <c r="G5" s="5">
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -2671,59 +2659,110 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21419039-3162-4ECA-8F2D-5A11BA84EEEC}">
-  <dimension ref="B2:F4"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F336CF09-ABF6-4B58-B238-B7578D6DF1E6}">
+  <dimension ref="B2:F7"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B2" s="4" t="s">
-        <v>492</v>
+        <v>243</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>493</v>
+        <v>464</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>494</v>
+        <v>465</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>495</v>
+        <v>466</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="3" spans="2:6" ht="34" x14ac:dyDescent="0.45">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="B3" s="5" t="s">
-        <v>497</v>
-      </c>
-      <c r="C3" s="13">
-        <v>0.52</v>
-      </c>
-      <c r="D3" s="13">
-        <v>0.57999999999999996</v>
+        <v>468</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>470</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>498</v>
+        <v>471</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" ht="34" x14ac:dyDescent="0.45">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="B4" s="5" t="s">
-        <v>500</v>
+        <v>473</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>501</v>
+        <v>474</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>502</v>
+        <v>475</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>503</v>
+        <v>476</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>504</v>
+        <v>477</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="B5" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="B6" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="B7" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>489</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>491</v>
       </c>
     </row>
   </sheetData>
@@ -2733,97 +2772,59 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A81CF7D8-E5E8-462A-A2F3-6690D175BB75}">
-  <dimension ref="B2:E7"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="3" max="3" width="12.6640625" customWidth="1"/>
-    <col min="4" max="4" width="23.83203125" customWidth="1"/>
-    <col min="5" max="5" width="15.4140625" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21419039-3162-4ECA-8F2D-5A11BA84EEEC}">
+  <dimension ref="B2:F4"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="2" spans="2:5" ht="34" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B2" s="4" t="s">
-        <v>152</v>
+        <v>492</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" ht="85" x14ac:dyDescent="0.45">
+        <v>495</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B3" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>508</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>509</v>
+        <v>497</v>
+      </c>
+      <c r="C3" s="13">
+        <v>0.52</v>
+      </c>
+      <c r="D3" s="13">
+        <v>0.57999999999999996</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" ht="102" x14ac:dyDescent="0.45">
+        <v>498</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B4" s="5" t="s">
-        <v>511</v>
+        <v>500</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>513</v>
+        <v>502</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" ht="85" x14ac:dyDescent="0.45">
-      <c r="B5" s="5" t="s">
-        <v>515</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>516</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>517</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" ht="85" x14ac:dyDescent="0.45">
-      <c r="B6" s="5" t="s">
-        <v>519</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>520</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>521</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" ht="68" x14ac:dyDescent="0.45">
-      <c r="B7" s="5" t="s">
-        <v>523</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>525</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>526</v>
+        <v>503</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>504</v>
       </c>
     </row>
   </sheetData>
@@ -2833,149 +2834,97 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{576AB1F0-4961-443E-9CB7-8832393C7A61}">
-  <dimension ref="B2:H7"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A81CF7D8-E5E8-462A-A2F3-6690D175BB75}">
+  <dimension ref="B2:E7"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="3" max="3" width="12.69921875" customWidth="1"/>
+    <col min="4" max="4" width="23.796875" customWidth="1"/>
+    <col min="5" max="5" width="15.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="34" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B2" s="4" t="s">
-        <v>243</v>
+        <v>152</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>527</v>
+        <v>505</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>528</v>
+        <v>506</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>464</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="3" spans="2:8" ht="68" x14ac:dyDescent="0.45">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B3" s="5" t="s">
-        <v>468</v>
+        <v>241</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>443</v>
+        <v>508</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>437</v>
+        <v>509</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>533</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" ht="51" x14ac:dyDescent="0.45">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B4" s="5" t="s">
-        <v>473</v>
+        <v>511</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>437</v>
+        <v>512</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>443</v>
+        <v>513</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>534</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>535</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" ht="34" x14ac:dyDescent="0.45">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" ht="52.2" x14ac:dyDescent="0.4">
       <c r="B5" s="5" t="s">
-        <v>478</v>
+        <v>515</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>443</v>
+        <v>516</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>443</v>
+        <v>517</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>443</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>536</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>537</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" ht="51" x14ac:dyDescent="0.45">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B6" s="5" t="s">
-        <v>538</v>
+        <v>519</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>443</v>
+        <v>520</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>437</v>
+        <v>521</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>539</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>540</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" ht="68" x14ac:dyDescent="0.45">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B7" s="5" t="s">
-        <v>542</v>
+        <v>523</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>443</v>
+        <v>524</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>443</v>
+        <v>525</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>443</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>543</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>544</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>545</v>
+        <v>526</v>
       </c>
     </row>
   </sheetData>
@@ -2985,11 +2934,163 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{576AB1F0-4961-443E-9CB7-8832393C7A61}">
+  <dimension ref="B2:H7"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="7" max="7" width="19" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="B2" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="B3" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>532</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="B4" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>535</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B5" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>536</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>537</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="B6" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>539</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>540</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="B7" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>544</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>545</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E4CDB66-C9CD-4433-9E32-190C4F7DC502}">
   <dimension ref="B2:E6"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="2" spans="2:5" ht="34" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
         <v>191</v>
       </c>
@@ -3003,7 +3104,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="3" spans="2:5" ht="68" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:5" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="B3" s="2" t="s">
         <v>461</v>
       </c>
@@ -3017,7 +3118,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="4" spans="2:5" ht="51" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:5" ht="52.2" x14ac:dyDescent="0.4">
       <c r="B4" s="2" t="s">
         <v>462</v>
       </c>
@@ -3031,7 +3132,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="51" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:5" ht="52.2" x14ac:dyDescent="0.4">
       <c r="B5" s="2" t="s">
         <v>463</v>
       </c>
@@ -3045,7 +3146,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="51" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:5" ht="52.2" x14ac:dyDescent="0.4">
       <c r="B6" s="2" t="s">
         <v>556</v>
       </c>
@@ -3068,16 +3169,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9F292E3-1024-4D5C-9FBC-A45132E1BC60}">
   <dimension ref="B2:G15"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" customWidth="1"/>
-    <col min="5" max="5" width="26.9140625" customWidth="1"/>
-    <col min="6" max="6" width="12.9140625" customWidth="1"/>
-    <col min="7" max="7" width="20.25" customWidth="1"/>
+    <col min="3" max="3" width="16.796875" customWidth="1"/>
+    <col min="4" max="4" width="18.296875" customWidth="1"/>
+    <col min="5" max="5" width="26.8984375" customWidth="1"/>
+    <col min="6" max="6" width="12.8984375" customWidth="1"/>
+    <col min="7" max="7" width="20.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="4" t="s">
         <v>35</v>
       </c>
@@ -3097,7 +3198,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="5" t="s">
         <v>41</v>
       </c>
@@ -3117,7 +3218,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="5" t="s">
         <v>41</v>
       </c>
@@ -3137,7 +3238,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="5" t="s">
         <v>41</v>
       </c>
@@ -3157,7 +3258,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="5" t="s">
         <v>41</v>
       </c>
@@ -3177,7 +3278,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="5" t="s">
         <v>41</v>
       </c>
@@ -3197,7 +3298,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="5" t="s">
         <v>64</v>
       </c>
@@ -3217,7 +3318,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="5" t="s">
         <v>64</v>
       </c>
@@ -3237,7 +3338,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="10" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="5" t="s">
         <v>64</v>
       </c>
@@ -3257,7 +3358,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="5" t="s">
         <v>77</v>
       </c>
@@ -3277,7 +3378,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="5" t="s">
         <v>77</v>
       </c>
@@ -3297,7 +3398,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="5" t="s">
         <v>77</v>
       </c>
@@ -3317,7 +3418,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="5" t="s">
         <v>77</v>
       </c>
@@ -3337,7 +3438,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="5" t="s">
         <v>77</v>
       </c>
@@ -3366,9 +3467,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96F1E14C-E7C1-4865-AE3D-B0CD9038CAB5}">
   <dimension ref="B2:J7"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="2" spans="2:10" ht="68" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:10" ht="52.2" x14ac:dyDescent="0.4">
       <c r="B2" s="4" t="s">
         <v>98</v>
       </c>
@@ -3397,7 +3498,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="3" spans="2:10" ht="102" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:10" ht="104.4" x14ac:dyDescent="0.4">
       <c r="B3" s="5" t="s">
         <v>107</v>
       </c>
@@ -3426,7 +3527,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="4" spans="2:10" ht="85" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:10" ht="87" x14ac:dyDescent="0.4">
       <c r="B4" s="5" t="s">
         <v>116</v>
       </c>
@@ -3455,7 +3556,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="5" spans="2:10" ht="68" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:10" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="B5" s="5" t="s">
         <v>125</v>
       </c>
@@ -3484,7 +3585,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="6" spans="2:10" ht="85" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:10" ht="87" x14ac:dyDescent="0.4">
       <c r="B6" s="5" t="s">
         <v>134</v>
       </c>
@@ -3513,7 +3614,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="7" spans="2:10" ht="68" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:10" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="B7" s="5" t="s">
         <v>143</v>
       </c>
@@ -3551,9 +3652,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89479098-1D22-42E9-AD3D-C407995A25F9}">
   <dimension ref="B2:H10"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="2" spans="2:8" ht="32" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:8" ht="31.2" x14ac:dyDescent="0.4">
       <c r="B2" s="7" t="s">
         <v>152</v>
       </c>
@@ -3576,7 +3677,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="112" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:8" ht="109.2" x14ac:dyDescent="0.4">
       <c r="B3" s="8" t="s">
         <v>159</v>
       </c>
@@ -3599,7 +3700,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="64" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:8" ht="62.4" x14ac:dyDescent="0.4">
       <c r="B4" s="8" t="s">
         <v>159</v>
       </c>
@@ -3622,7 +3723,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="80" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:8" ht="78" x14ac:dyDescent="0.4">
       <c r="B5" s="8" t="s">
         <v>167</v>
       </c>
@@ -3645,7 +3746,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="64" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:8" ht="62.4" x14ac:dyDescent="0.4">
       <c r="B6" s="8" t="s">
         <v>167</v>
       </c>
@@ -3668,7 +3769,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="80" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:8" ht="78" x14ac:dyDescent="0.4">
       <c r="B7" s="8" t="s">
         <v>174</v>
       </c>
@@ -3691,7 +3792,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="64" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:8" ht="62.4" x14ac:dyDescent="0.4">
       <c r="B8" s="8" t="s">
         <v>174</v>
       </c>
@@ -3714,7 +3815,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="64" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:8" ht="62.4" x14ac:dyDescent="0.4">
       <c r="B9" s="8" t="s">
         <v>174</v>
       </c>
@@ -3737,7 +3838,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="64" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:8" ht="62.4" x14ac:dyDescent="0.4">
       <c r="B10" s="8" t="s">
         <v>184</v>
       </c>
@@ -3770,17 +3871,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21A7A804-F3A0-4FE1-BBA0-D32DD3EC425E}">
   <dimension ref="B2:G10"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.796875" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="27.08203125" customWidth="1"/>
-    <col min="5" max="5" width="7.4140625" customWidth="1"/>
-    <col min="6" max="6" width="8.6640625" customWidth="1"/>
-    <col min="7" max="7" width="29.08203125" customWidth="1"/>
+    <col min="4" max="4" width="27.09765625" customWidth="1"/>
+    <col min="5" max="5" width="7.3984375" customWidth="1"/>
+    <col min="6" max="6" width="8.69921875" customWidth="1"/>
+    <col min="7" max="7" width="29.09765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="29" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:7" ht="26.4" x14ac:dyDescent="0.4">
       <c r="B2" s="9" t="s">
         <v>188</v>
       </c>
@@ -3800,7 +3901,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="3" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="10" t="s">
         <v>194</v>
       </c>
@@ -3820,7 +3921,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="4" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="10" t="s">
         <v>200</v>
       </c>
@@ -3840,7 +3941,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="5" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="10" t="s">
         <v>206</v>
       </c>
@@ -3860,7 +3961,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="10" t="s">
         <v>211</v>
       </c>
@@ -3880,7 +3981,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>217</v>
       </c>
@@ -3900,7 +4001,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="8" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>222</v>
       </c>
@@ -3920,7 +4021,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="9" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="10" t="s">
         <v>227</v>
       </c>
@@ -3940,7 +4041,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="10" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>232</v>
       </c>
@@ -3969,17 +4070,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71243D3E-E821-4CDB-B47E-04773EBD590B}">
   <dimension ref="B2:I10"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="12.1640625" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" customWidth="1"/>
-    <col min="5" max="5" width="10.9140625" customWidth="1"/>
-    <col min="6" max="6" width="18.58203125" customWidth="1"/>
-    <col min="8" max="8" width="14.33203125" customWidth="1"/>
-    <col min="9" max="9" width="18.08203125" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" customWidth="1"/>
+    <col min="3" max="3" width="11.69921875" customWidth="1"/>
+    <col min="5" max="5" width="10.8984375" customWidth="1"/>
+    <col min="6" max="6" width="18.59765625" customWidth="1"/>
+    <col min="8" max="8" width="14.296875" customWidth="1"/>
+    <col min="9" max="9" width="18.09765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="9" t="s">
         <v>238</v>
       </c>
@@ -4005,7 +4106,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="3" spans="2:9" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="10" t="s">
         <v>245</v>
       </c>
@@ -4031,7 +4132,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="4" spans="2:9" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="10" t="s">
         <v>253</v>
       </c>
@@ -4057,7 +4158,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="10" t="s">
         <v>261</v>
       </c>
@@ -4083,7 +4184,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="10" t="s">
         <v>269</v>
       </c>
@@ -4109,7 +4210,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="10" t="s">
         <v>277</v>
       </c>
@@ -4135,7 +4236,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="10" t="s">
         <v>284</v>
       </c>
@@ -4161,7 +4262,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="10" t="s">
         <v>292</v>
       </c>
@@ -4187,7 +4288,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="10" spans="2:9" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="10" t="s">
         <v>299</v>
       </c>
@@ -4222,17 +4323,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D73D6497-7B11-4E25-9D30-9BDA54598956}">
   <dimension ref="B2:G12"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="11.33203125" customWidth="1"/>
-    <col min="3" max="3" width="24.83203125" customWidth="1"/>
-    <col min="4" max="4" width="37.1640625" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="11.296875" customWidth="1"/>
+    <col min="3" max="3" width="24.796875" customWidth="1"/>
+    <col min="4" max="4" width="37.19921875" customWidth="1"/>
+    <col min="5" max="5" width="15.69921875" customWidth="1"/>
     <col min="6" max="6" width="17.5" customWidth="1"/>
-    <col min="7" max="7" width="25.6640625" customWidth="1"/>
+    <col min="7" max="7" width="25.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="4" t="s">
         <v>306</v>
       </c>
@@ -4252,7 +4353,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="3" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="5" t="s">
         <v>310</v>
       </c>
@@ -4272,7 +4373,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="4" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="5" t="s">
         <v>316</v>
       </c>
@@ -4292,7 +4393,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="5" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="5" t="s">
         <v>322</v>
       </c>
@@ -4312,7 +4413,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="5" t="s">
         <v>328</v>
       </c>
@@ -4332,7 +4433,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="5" t="s">
         <v>334</v>
       </c>
@@ -4352,7 +4453,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="8" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="5" t="s">
         <v>340</v>
       </c>
@@ -4372,7 +4473,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="9" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="5" t="s">
         <v>346</v>
       </c>
@@ -4392,7 +4493,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="10" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="5" t="s">
         <v>352</v>
       </c>
@@ -4412,7 +4513,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="11" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="5" t="s">
         <v>358</v>
       </c>
@@ -4432,7 +4533,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="5" t="s">
         <v>364</v>
       </c>
@@ -4461,15 +4562,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{605D9EF7-9336-46D1-A1D5-1FCFEA05638F}">
   <dimension ref="B2:F14"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="20.5" customWidth="1"/>
-    <col min="4" max="4" width="12.08203125" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.09765625" customWidth="1"/>
+    <col min="5" max="5" width="10.796875" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="11" t="s">
         <v>370</v>
       </c>
@@ -4486,7 +4587,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="3" spans="2:6" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="12" t="s">
         <v>374</v>
       </c>
@@ -4503,7 +4604,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="4" spans="2:6" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="12" t="s">
         <v>379</v>
       </c>
@@ -4520,7 +4621,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="12" t="s">
         <v>384</v>
       </c>
@@ -4537,7 +4638,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="12" t="s">
         <v>389</v>
       </c>
@@ -4554,7 +4655,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="12" t="s">
         <v>394</v>
       </c>
@@ -4571,7 +4672,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="12" t="s">
         <v>399</v>
       </c>
@@ -4588,7 +4689,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="12" t="s">
         <v>404</v>
       </c>
@@ -4605,7 +4706,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="12" t="s">
         <v>408</v>
       </c>
@@ -4622,7 +4723,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="12" t="s">
         <v>413</v>
       </c>
@@ -4639,7 +4740,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="12" t="s">
         <v>418</v>
       </c>
@@ -4656,7 +4757,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="12" t="s">
         <v>422</v>
       </c>
@@ -4673,7 +4774,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="40" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="12" t="s">
         <v>426</v>
       </c>
@@ -4697,108 +4798,92 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D7B6EB1-DF05-4E63-BE4E-F700AD81F457}">
-  <dimension ref="B2:G6"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F014EF38-B579-4298-8036-972AFC854C88}">
+  <dimension ref="B3:E8"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="2" spans="2:7" ht="34" x14ac:dyDescent="0.45">
-      <c r="B2" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>431</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" ht="34" x14ac:dyDescent="0.45">
-      <c r="B3" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>438</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>440</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="51" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B3" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" ht="87" x14ac:dyDescent="0.4">
       <c r="B4" s="5" t="s">
-        <v>442</v>
+        <v>241</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>443</v>
+        <v>508</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>392</v>
+        <v>509</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>444</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>445</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="51" x14ac:dyDescent="0.45">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" ht="104.4" x14ac:dyDescent="0.4">
       <c r="B5" s="5" t="s">
-        <v>447</v>
+        <v>511</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>437</v>
+        <v>512</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>448</v>
+        <v>513</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" ht="34" x14ac:dyDescent="0.45">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" ht="87" x14ac:dyDescent="0.4">
       <c r="B6" s="5" t="s">
-        <v>451</v>
+        <v>515</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>443</v>
+        <v>516</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>392</v>
+        <v>517</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>452</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>454</v>
+        <v>518</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="87" x14ac:dyDescent="0.4">
+      <c r="B7" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>520</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>521</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="B8" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>526</v>
       </c>
     </row>
   </sheetData>
